--- a/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:43:11+00:00</t>
+    <t>2026-09-14T07:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:43:38+00:00</t>
+    <t>2026-10-01T07:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T07:35:36+00:00</t>
+    <t>2026-10-14T13:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Cette section regroupe les rÃ©sultats d'examens (biologie polyvalente, imagerie, cytologie, pathologie, gÃ©nÃ©tique humaine...)</t>
+    <t>Cette section regroupe les résultats d'examens (biologie polyvalente, imagerie, cytologie, pathologie, génétique humaine...)</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -411,7 +411,7 @@
     <t>frSectionResultats</t>
   </si>
   <si>
-    <t>ConformitÃ© de la section aux spÃ©cifications CI-SIS</t>
+    <t>Conformité de la section aux spécifications CI-SIS</t>
   </si>
   <si>
     <t>Section.templateId:frSectionResultats.nullFlavor</t>
@@ -563,7 +563,7 @@
     <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
   </si>
   <si>
-    <t>RÃ©sultats dâ€™examens</t>
+    <t>Résultats d’examens</t>
   </si>
   <si>
     <t>CD.displayName</t>
@@ -729,7 +729,7 @@
 </t>
   </si>
   <si>
-    <t>EntrÃ©e FR-Resultats</t>
+    <t>Entrée FR-Resultats</t>
   </si>
   <si>
     <t>Section.entry.nullFlavor</t>

--- a/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:15:36+00:00</t>
+    <t>2026-10-15T09:41:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:41:25+00:00</t>
+    <t>2026-10-15T10:11:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:11:14+00:00</t>
+    <t>2026-10-15T11:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:51:04+00:00</t>
+    <t>2026-10-15T13:36:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:36:09+00:00</t>
+    <t>2026-10-15T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:46:20+00:00</t>
+    <t>2026-10-16T07:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:40:35+00:00</t>
+    <t>2026-10-16T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:34:24+00:00</t>
+    <t>2026-10-16T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-section-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:04:08+00:00</t>
+    <t>2026-10-16T11:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
